--- a/test.xlsx
+++ b/test.xlsx
@@ -419,7 +419,7 @@
     <col min="3" max="3" width="10" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
+    <row r="1" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -437,7 +437,9 @@
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="3">
+        <v>44403.871640474536</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="1" gridLines="1"/>

--- a/test.xlsx
+++ b/test.xlsx
@@ -438,7 +438,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="3">
-        <v>44403.871640474536</v>
+        <v>44403.88447167824</v>
       </c>
     </row>
   </sheetData>

--- a/test.xlsx
+++ b/test.xlsx
@@ -4,28 +4,11 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Data" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="Summary" state="visible" r:id="rId3"/>
+    <sheet sheetId="2" name="Data" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>D.O.B.</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -55,9 +38,18 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0000FF"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -67,11 +59,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,7 +404,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -420,29 +412,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
+      <c r="A1" s="1" t="str">
+        <v>Id</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" s="3" t="str">
+        <v>D.O.B.</v>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
+      <c r="B2" s="4" t="str">
+        <v>Test</v>
       </c>
       <c r="C2" s="3">
-        <v>44403.88447167824</v>
+        <v>44403.92390743055</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -450,10 +441,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData/>
-  <printOptions headings="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/test.xlsx
+++ b/test.xlsx
@@ -30,20 +30,36 @@
       <name val="Comic Sans"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF00FF00"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -59,12 +75,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,8 +446,8 @@
       <c r="B2" s="4" t="str">
         <v>Test</v>
       </c>
-      <c r="C2" s="3">
-        <v>44403.92390743055</v>
+      <c r="C2" s="5">
+        <v>44404.602394050926</v>
       </c>
     </row>
   </sheetData>

--- a/test.xlsx
+++ b/test.xlsx
@@ -13,11 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0.00;[Red]-&quot;£&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -25,47 +21,18 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <name val="Comic Sans"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="double">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF00FF00"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF0000FF"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -75,13 +42,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,34 +384,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10" style="3" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="str">
-        <v>Id</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>D.O.B.</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>24</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>Test</v>
-      </c>
-      <c r="C2" s="5">
-        <v>44404.602394050926</v>
-      </c>
-    </row>
+    <row r="1" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/test.xlsx
+++ b/test.xlsx
@@ -35,11 +35,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF0000FF"/>
         <bgColor rgb="FF0000FF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -58,14 +59,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,68 +429,68 @@
     <col min="16" max="21" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="str">
+    <row r="1" ht="42" customHeight="1" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="str">
         <v>COL 0</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" s="3" t="str">
         <v>COL 1</v>
       </c>
-      <c r="C1" s="2" t="str">
+      <c r="C1" s="5" t="str">
         <v>COL 2</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" s="3" t="str">
         <v>COL 3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" s="3" t="str">
         <v>COL 4</v>
       </c>
-      <c r="F1" s="1" t="str">
+      <c r="F1" s="4" t="str">
         <v>COL 5</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" s="3" t="str">
         <v>COL 6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="H1" s="3" t="str">
         <v>COL 7</v>
       </c>
-      <c r="I1" s="2" t="str">
+      <c r="I1" s="5" t="str">
         <v>COL 8</v>
       </c>
-      <c r="J1" t="str">
+      <c r="J1" s="3" t="str">
         <v>COL 9</v>
       </c>
-      <c r="K1" s="1" t="str">
+      <c r="K1" s="4" t="str">
         <v>COL 10</v>
       </c>
-      <c r="L1" t="str">
+      <c r="L1" s="3" t="str">
         <v>COL 11</v>
       </c>
-      <c r="M1" t="str">
+      <c r="M1" s="3" t="str">
         <v>COL 12</v>
       </c>
-      <c r="N1" t="str">
+      <c r="N1" s="3" t="str">
         <v>COL 13</v>
       </c>
-      <c r="O1" s="2" t="str">
+      <c r="O1" s="5" t="str">
         <v>COL 14</v>
       </c>
-      <c r="P1" s="1" t="str">
+      <c r="P1" s="4" t="str">
         <v>COL 15</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="Q1" s="3" t="str">
         <v>COL 16</v>
       </c>
-      <c r="R1" t="str">
+      <c r="R1" s="3" t="str">
         <v>COL 17</v>
       </c>
-      <c r="S1" t="str">
+      <c r="S1" s="3" t="str">
         <v>COL 18</v>
       </c>
-      <c r="T1" t="str">
+      <c r="T1" s="3" t="str">
         <v>COL 19</v>
       </c>
-      <c r="U1" s="1" t="str">
+      <c r="U1" s="4" t="str">
         <v>COL 20</v>
       </c>
     </row>
